--- a/Personal_Logs/Movie_Watch_List.xlsx
+++ b/Personal_Logs/Movie_Watch_List.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Movie_Watch_List" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Movie_Watch_List!$C$1:$C$7</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="80">
   <si>
     <t>片名</t>
   </si>
@@ -39,25 +42,295 @@
     <t>观看日期</t>
   </si>
   <si>
+    <t>中国香港</t>
+  </si>
+  <si>
+    <t>哪吒之魔童闹海</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>五个扑水的少年</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>招魂</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>死寂</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白蛇2：青蛇劫起</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔卡少女樱剧场版：被封印的卡片</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔卡少女樱剧场版：香港篇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>南极之恋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>与恐龙同行</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>英国/美国/澳大利亚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>唐人街探案3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沐浴之王</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个杀手不太冷静</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>扬名立万</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>失控玩家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国/加拿大</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘海域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>头号玩家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>门锁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>守岛人</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人在囧途</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪灵</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>英国/美国</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>触不可及</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>法国</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人生大事</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>消失的她</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜救</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇迹·笨小孩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>误杀2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大鱼</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>监狱风云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国香港</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>神奇动物在哪里</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疯狂元素城</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>九品芝麻官之白面包青天</t>
-  </si>
-  <si>
-    <t>中国香港</t>
-  </si>
-  <si>
-    <t>哪吒之魔童闹海</t>
-  </si>
-  <si>
-    <t>中国</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1297518/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/34780991/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>小林家的龙女仆：怕寂寞的龙</t>
-  </si>
-  <si>
-    <t>日本</t>
-  </si>
-  <si>
-    <t>百变小樱剧场版：香港篇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/37037980/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/3117775/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/3117778/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/26628329/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1895120/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1422162/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35030151/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/3804629/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/30435124/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/27619748/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35901878/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/25726614/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1293422/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/34991572/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35312437/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35068653/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35660795/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35460157/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/6786002/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1292225/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/4237879/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35073565/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35073565/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/4920389/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/3822687/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/30337388/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35422807/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35505100/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/34894753/</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -65,7 +338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,6 +498,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,7 +805,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -650,8 +932,11 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -661,8 +946,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -688,6 +976,7 @@
     <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="42" builtinId="8"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
@@ -982,17 +1271,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="49.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1011,84 +1302,786 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
-        <v>34424</v>
+        <v>41628</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>45865</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44354</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2">
+        <v>43132</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2">
-        <v>45686</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" s="1">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="E3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>45886</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44461</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>45835</v>
+        <v>44470</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44501</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2">
+        <v>41433</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1">
+        <v>112</v>
+      </c>
+      <c r="E5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>44510</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>39157</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1">
+        <v>89</v>
+      </c>
+      <c r="E6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>44511</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2">
+        <v>44400</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>131</v>
+      </c>
+      <c r="E7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>44513</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2">
+        <v>44239</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>136</v>
+      </c>
+      <c r="E8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>44535</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2">
+        <v>44176</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>103</v>
+      </c>
+      <c r="E9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>44546</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2">
+        <v>44593</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>109</v>
+      </c>
+      <c r="E10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>44620</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2">
+        <v>44511</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1">
+        <v>123</v>
+      </c>
+      <c r="E11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>44662</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2">
+        <v>44435</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1">
+        <v>115</v>
+      </c>
+      <c r="E12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>44683</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2">
+        <v>44634</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <v>116</v>
+      </c>
+      <c r="E13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>44733</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2">
+        <v>43189</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1">
+        <v>140</v>
+      </c>
+      <c r="E14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>44798</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2">
+        <v>44519</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1">
+        <v>105</v>
+      </c>
+      <c r="E15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>44899</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2">
+        <v>44365</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>125</v>
+      </c>
+      <c r="E16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>45189</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2">
+        <v>40333</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1">
+        <v>91</v>
+      </c>
+      <c r="E17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>45197</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2">
+        <v>29385</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="1">
+        <v>146</v>
+      </c>
+      <c r="E18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>45247</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2">
+        <v>40849</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="1">
+        <v>112</v>
+      </c>
+      <c r="E19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>45283</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>44736</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>112</v>
+      </c>
+      <c r="E20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>45287</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1">
+        <v>121</v>
+      </c>
+      <c r="E21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>45361</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>44837</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1">
+        <v>108</v>
+      </c>
+      <c r="E22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="2">
+        <v>44547</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1">
+        <v>118</v>
+      </c>
+      <c r="E23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>45364</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="2">
+        <v>44593</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1">
+        <v>106</v>
+      </c>
+      <c r="E24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>45366</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2">
+        <v>43919</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="1">
+        <v>95</v>
+      </c>
+      <c r="E25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>32094</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1">
+        <v>101</v>
+      </c>
+      <c r="E26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45386</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2">
+        <v>42699</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="1">
+        <v>133</v>
+      </c>
+      <c r="E27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45407</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45093</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1">
+        <v>102</v>
+      </c>
+      <c r="E28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45467</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="2">
+        <v>34424</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1">
+        <v>108</v>
+      </c>
+      <c r="E29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>45865</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1">
+        <v>144</v>
+      </c>
+      <c r="E30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45886</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45835</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1">
+        <v>105</v>
+      </c>
+      <c r="E31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>46100</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2">
         <v>36393</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1">
         <v>81</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="E32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>46237</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="2">
+        <v>36722</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1">
+        <v>82</v>
+      </c>
+      <c r="E33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>46244</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="A2:F35">
+    <sortCondition ref="F2:F35"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G29" r:id="rId1"/>
+    <hyperlink ref="G30" r:id="rId2"/>
+    <hyperlink ref="G31" r:id="rId3"/>
+    <hyperlink ref="G32" r:id="rId4"/>
+    <hyperlink ref="G33" r:id="rId5"/>
+    <hyperlink ref="G2" r:id="rId6"/>
+    <hyperlink ref="G3" r:id="rId7"/>
+    <hyperlink ref="G6" r:id="rId8"/>
+    <hyperlink ref="G4" r:id="rId9"/>
+    <hyperlink ref="G5" r:id="rId10"/>
+    <hyperlink ref="G7" r:id="rId11"/>
+    <hyperlink ref="G8" r:id="rId12"/>
+    <hyperlink ref="G28" r:id="rId13"/>
+    <hyperlink ref="G27" r:id="rId14"/>
+    <hyperlink ref="G26" r:id="rId15"/>
+    <hyperlink ref="G25" r:id="rId16"/>
+    <hyperlink ref="G24" r:id="rId17"/>
+    <hyperlink ref="G23" r:id="rId18"/>
+    <hyperlink ref="G22" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G20" r:id="rId21"/>
+    <hyperlink ref="G19" r:id="rId22"/>
+    <hyperlink ref="G18" r:id="rId23"/>
+    <hyperlink ref="G17" r:id="rId24"/>
+    <hyperlink ref="G16" r:id="rId25"/>
+    <hyperlink ref="G15" r:id="rId26"/>
+    <hyperlink ref="G14" r:id="rId27"/>
+    <hyperlink ref="G13" r:id="rId28"/>
+    <hyperlink ref="G12" r:id="rId29"/>
+    <hyperlink ref="G11" r:id="rId30"/>
+    <hyperlink ref="G10" r:id="rId31"/>
+    <hyperlink ref="G9" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
 </worksheet>
 </file>